--- a/data/nursing_home/data.xlsx
+++ b/data/nursing_home/data.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:N12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -448,16 +448,16 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>34.33546278</v>
+        <v>34.34519278</v>
       </c>
       <c r="C2" t="str">
-        <v>134.0347836</v>
+        <v>134.0663553</v>
       </c>
       <c r="D2" t="str">
-        <v>ケアサポート長谷川（中央西）</v>
+        <v>ケアサポート長谷川（中央東）</v>
       </c>
       <c r="E2" t="str">
-        <v>高松市宮脇町二丁目26-12</v>
+        <v>高松市福岡町二丁目16-6　福岡事業所１階</v>
       </c>
       <c r="F2" t="str">
         <v/>
@@ -492,16 +492,16 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>34.34519278</v>
+        <v>34.28475389</v>
       </c>
       <c r="C3" t="str">
-        <v>134.0663553</v>
+        <v>134.0029683</v>
       </c>
       <c r="D3" t="str">
-        <v>ケアサポート長谷川（中央東）</v>
+        <v>えんざ</v>
       </c>
       <c r="E3" t="str">
-        <v>高松市福岡町二丁目16-6　福岡事業所１階</v>
+        <v>高松市西山崎町196-2</v>
       </c>
       <c r="F3" t="str">
         <v/>
@@ -536,16 +536,16 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>34.28475389</v>
+        <v>34.3215625</v>
       </c>
       <c r="C4" t="str">
-        <v>134.0029683</v>
+        <v>134.0749803</v>
       </c>
       <c r="D4" t="str">
-        <v>えんざ</v>
+        <v>小規模多機能ホームたんぽぽの家</v>
       </c>
       <c r="E4" t="str">
-        <v>高松市西山崎町196-2</v>
+        <v>高松市木太町1539-8</v>
       </c>
       <c r="F4" t="str">
         <v/>
@@ -580,16 +580,16 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>34.3215625</v>
+        <v>34.31648028</v>
       </c>
       <c r="C5" t="str">
-        <v>134.0749803</v>
+        <v>134.1022917</v>
       </c>
       <c r="D5" t="str">
-        <v>小規模多機能ホームたんぽぽの家</v>
+        <v>ケアサポート長谷川（古高松）</v>
       </c>
       <c r="E5" t="str">
-        <v>高松市木太町1539-8</v>
+        <v>高松市新田町甲2181-1</v>
       </c>
       <c r="F5" t="str">
         <v/>
@@ -624,16 +624,16 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>34.31648028</v>
+        <v>34.35848056</v>
       </c>
       <c r="C6" t="str">
-        <v>134.1022917</v>
+        <v>134.0891589</v>
       </c>
       <c r="D6" t="str">
-        <v>ケアサポート長谷川（古高松）</v>
+        <v>小規模多機能施設　富士</v>
       </c>
       <c r="E6" t="str">
-        <v>高松市新田町甲2181-1</v>
+        <v>高松市屋島西町2277-4</v>
       </c>
       <c r="F6" t="str">
         <v/>
@@ -668,16 +668,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>34.35848056</v>
+        <v>34.2964575</v>
       </c>
       <c r="C7" t="str">
-        <v>134.0891589</v>
+        <v>134.0994817</v>
       </c>
       <c r="D7" t="str">
-        <v>小規模多機能施設　富士</v>
+        <v>多機能型施設  邑</v>
       </c>
       <c r="E7" t="str">
-        <v>高松市屋島西町2277-4</v>
+        <v>高松市前田西町1080-18</v>
       </c>
       <c r="F7" t="str">
         <v/>
@@ -712,16 +712,16 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>34.2964575</v>
+        <v>34.27412639</v>
       </c>
       <c r="C8" t="str">
-        <v>134.0994817</v>
+        <v>134.0882281</v>
       </c>
       <c r="D8" t="str">
-        <v>多機能型施設  邑</v>
+        <v>香川県高齢者生活協同組合「ひだまり川島」</v>
       </c>
       <c r="E8" t="str">
-        <v>高松市前田西町1080-18</v>
+        <v>高松市川島東町925-1</v>
       </c>
       <c r="F8" t="str">
         <v/>
@@ -756,16 +756,16 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>34.27412639</v>
+        <v>34.27728694</v>
       </c>
       <c r="C9" t="str">
-        <v>134.0882281</v>
+        <v>134.0755206</v>
       </c>
       <c r="D9" t="str">
-        <v>香川県高齢者生活協同組合「ひだまり川島」</v>
+        <v>やまぶき小規模多機能型居宅介護事業所</v>
       </c>
       <c r="E9" t="str">
-        <v>高松市川島東町925-1</v>
+        <v>高松市三谷町316</v>
       </c>
       <c r="F9" t="str">
         <v/>
@@ -800,16 +800,16 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>34.27728694</v>
+        <v>34.35680056</v>
       </c>
       <c r="C10" t="str">
-        <v>134.0755206</v>
+        <v>133.9730411</v>
       </c>
       <c r="D10" t="str">
-        <v>やまぶき小規模多機能型居宅介護事業所</v>
+        <v>在宅サポートセンター　ハピネス</v>
       </c>
       <c r="E10" t="str">
-        <v>高松市三谷町316</v>
+        <v>高松市中山町772-1</v>
       </c>
       <c r="F10" t="str">
         <v/>
@@ -844,16 +844,16 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>34.35680056</v>
+        <v>34.32090611</v>
       </c>
       <c r="C11" t="str">
-        <v>133.9730411</v>
+        <v>134.1599506</v>
       </c>
       <c r="D11" t="str">
-        <v>在宅サポートセンター　ハピネス</v>
+        <v>小規模多機能型施設  侶</v>
       </c>
       <c r="E11" t="str">
-        <v>高松市中山町772-1</v>
+        <v>高松市牟礼町原216-5</v>
       </c>
       <c r="F11" t="str">
         <v/>
@@ -888,16 +888,16 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>34.32090611</v>
+        <v>34.264656</v>
       </c>
       <c r="C12" t="str">
-        <v>134.1599506</v>
+        <v>134.02725</v>
       </c>
       <c r="D12" t="str">
-        <v>小規模多機能型施設  侶</v>
+        <v>多機能ホーム　ひまわり</v>
       </c>
       <c r="E12" t="str">
-        <v>高松市牟礼町原216-5</v>
+        <v>高松市香川町大野901-1</v>
       </c>
       <c r="F12" t="str">
         <v/>
@@ -924,56 +924,12 @@
         <v/>
       </c>
       <c r="N12" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>12</v>
-      </c>
-      <c r="B13" t="str">
-        <v>34.264656</v>
-      </c>
-      <c r="C13" t="str">
-        <v>134.02725</v>
-      </c>
-      <c r="D13" t="str">
-        <v>多機能ホーム　ひまわり</v>
-      </c>
-      <c r="E13" t="str">
-        <v>高松市香川町大野901-1</v>
-      </c>
-      <c r="F13" t="str">
-        <v/>
-      </c>
-      <c r="G13" t="str">
-        <v/>
-      </c>
-      <c r="H13" t="str">
-        <v/>
-      </c>
-      <c r="I13" t="str">
-        <v>小規模多機能型居宅介護</v>
-      </c>
-      <c r="J13" t="str">
-        <v/>
-      </c>
-      <c r="K13" t="str">
-        <v/>
-      </c>
-      <c r="L13" t="str">
-        <v/>
-      </c>
-      <c r="M13" t="str">
-        <v/>
-      </c>
-      <c r="N13" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N13"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N12"/>
   </ignoredErrors>
 </worksheet>
 </file>